--- a/Excel_pnd1k/excel_data_pnd1k.xlsx
+++ b/Excel_pnd1k/excel_data_pnd1k.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6becf00b5c44c692/เอกสาร/GitHub/Bot_Server/Excel_pnd1k/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="695" documentId="8_{E62BB257-A0A0-4383-8146-1EEB7D39A510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0A7EAAA-81B7-4C31-8AFF-00C179B0292E}"/>
+  <xr:revisionPtr revIDLastSave="3335" documentId="8_{E62BB257-A0A0-4383-8146-1EEB7D39A510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E71723C-E567-43DA-9CEB-AA80FF0638C0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-930" windowWidth="29040" windowHeight="15720" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="5" state="hidden" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="133">
   <si>
     <t>ชื่อ</t>
   </si>
@@ -575,22 +575,19 @@
     <t xml:space="preserve">อ </t>
   </si>
   <si>
-    <t>บริษัท ไอสาม เกทเวย์ จำกัด รายเดือน</t>
-  </si>
-  <si>
-    <t>อาคาร ไอทีเอฟ-ทาวเวอร์ ชั้นที่ 25 เลขที่ 140/61 ถนน สีลม ตำบล/แขวง สุริยวงศ์ อำเภอ/เขต บางรัก จังหวัด กรุงเทพมหานคร 10500</t>
-  </si>
-  <si>
     <t>31/12/2025</t>
   </si>
   <si>
-    <t>คุณ ณจิตตา วัฒนาภรณ์</t>
+    <t>บริษัท เน็กซ์สเต็ป แมเนจเม้นท์ จำกัด รายเดือน</t>
   </si>
   <si>
-    <t>400 ซ.บางบอน 5 ซอย 12 แขวงบางบอนเหนือ เขตบางบอน กรุงเทพมหานคร</t>
+    <t>เลขที่ 633 ตรอก/ซอย อ่อนนุช30 ตำบล/แขวง ออนนุช อำเภอ/เขต สวนหลวง จังหวัด กรุงเทพมหานคร 10250</t>
   </si>
   <si>
-    <t>หนึ่งหมื่นสองพันห้าร้อยหกสิบเจ็ดบาทสามสิบสามสตางค์</t>
+    <t>ศูนย์บาทถ้วน</t>
+  </si>
+  <si>
+    <t>นาย อภิวัฒน์ บ้านมอญ</t>
   </si>
 </sst>
 </file>
@@ -6909,23 +6906,23 @@
       <c r="AN8" s="219"/>
       <c r="AO8" s="166"/>
       <c r="AP8" s="213">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ8" s="214"/>
       <c r="AR8" s="214">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS8" s="214"/>
       <c r="AT8" s="214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU8" s="214"/>
       <c r="AV8" s="214">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW8" s="214"/>
       <c r="AX8" s="214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY8" s="219"/>
       <c r="AZ8" s="166"/>
@@ -6934,12 +6931,12 @@
       </c>
       <c r="BB8" s="214"/>
       <c r="BC8" s="214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BD8" s="219"/>
       <c r="BE8" s="166"/>
       <c r="BF8" s="216">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BG8" s="217"/>
       <c r="BH8" s="102"/>
@@ -6984,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="235" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" s="235"/>
       <c r="F10" s="235"/>
@@ -7069,7 +7066,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="233" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" s="233"/>
       <c r="F12" s="233"/>
@@ -7339,7 +7336,7 @@
       </c>
       <c r="AQ16" s="214"/>
       <c r="AR16" s="214">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS16" s="214"/>
       <c r="AT16" s="214">
@@ -7347,25 +7344,25 @@
       </c>
       <c r="AU16" s="214"/>
       <c r="AV16" s="214">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AW16" s="214"/>
       <c r="AX16" s="214">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY16" s="219"/>
       <c r="AZ16" s="166"/>
       <c r="BA16" s="213">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB16" s="214"/>
       <c r="BC16" s="214">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD16" s="219"/>
       <c r="BE16" s="166"/>
       <c r="BF16" s="216">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BG16" s="217"/>
       <c r="BH16" s="102"/>
@@ -7417,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="234" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18" s="234"/>
       <c r="F18" s="234"/>
@@ -7502,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="232" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E20" s="233"/>
       <c r="F20" s="233"/>
@@ -8097,7 +8094,7 @@
       <c r="AI30" s="93"/>
       <c r="AJ30" s="93"/>
       <c r="AK30" s="299" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AL30" s="300"/>
       <c r="AM30" s="300"/>
@@ -8107,7 +8104,7 @@
       <c r="AQ30" s="300"/>
       <c r="AR30" s="301"/>
       <c r="AS30" s="326">
-        <v>488100</v>
+        <v>6000</v>
       </c>
       <c r="AT30" s="327"/>
       <c r="AU30" s="327"/>
@@ -8117,7 +8114,7 @@
       <c r="AY30" s="327"/>
       <c r="AZ30" s="328"/>
       <c r="BA30" s="336">
-        <v>12567.33</v>
+        <v>0</v>
       </c>
       <c r="BB30" s="337"/>
       <c r="BC30" s="337"/>
@@ -9659,7 +9656,7 @@
       </c>
       <c r="AR54" s="135"/>
       <c r="AS54" s="188">
-        <v>488100</v>
+        <v>6000</v>
       </c>
       <c r="AT54" s="189"/>
       <c r="AU54" s="189"/>
@@ -9669,7 +9666,7 @@
       <c r="AY54" s="189"/>
       <c r="AZ54" s="251"/>
       <c r="BA54" s="188">
-        <v>12567.33</v>
+        <v>0</v>
       </c>
       <c r="BB54" s="189"/>
       <c r="BC54" s="189"/>
@@ -9749,7 +9746,7 @@
         <v>37</v>
       </c>
       <c r="P56" s="261" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q56" s="262"/>
       <c r="R56" s="262"/>
@@ -9908,7 +9905,7 @@
         <v>75</v>
       </c>
       <c r="AM58" s="330">
-        <v>9000</v>
+        <v>750</v>
       </c>
       <c r="AN58" s="330"/>
       <c r="AO58" s="330"/>
@@ -10408,7 +10405,7 @@
       <c r="N67" s="158"/>
       <c r="Z67" s="159"/>
       <c r="AI67" s="238" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AJ67" s="238"/>
       <c r="AK67" s="238"/>
@@ -10974,27 +10971,27 @@
       <c r="AO82" s="166"/>
       <c r="AP82" s="213">
         <f>AP8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ82" s="214"/>
       <c r="AR82" s="214">
         <f>AR8</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS82" s="214"/>
       <c r="AT82" s="214">
         <f>AT8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU82" s="214"/>
       <c r="AV82" s="214">
         <f>AV8</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW82" s="214"/>
       <c r="AX82" s="214">
         <f>AX8</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY82" s="219"/>
       <c r="AZ82" s="166"/>
@@ -11005,13 +11002,13 @@
       <c r="BB82" s="214"/>
       <c r="BC82" s="214">
         <f>BC8</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BD82" s="219"/>
       <c r="BE82" s="166"/>
       <c r="BF82" s="216">
         <f>BF8</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BG82" s="217"/>
       <c r="BH82" s="102"/>
@@ -11057,7 +11054,7 @@
       </c>
       <c r="D84" s="235" t="str">
         <f>D10</f>
-        <v>บริษัท ไอสาม เกทเวย์ จำกัด รายเดือน</v>
+        <v>บริษัท เน็กซ์สเต็ป แมเนจเม้นท์ จำกัด รายเดือน</v>
       </c>
       <c r="E84" s="235"/>
       <c r="F84" s="235"/>
@@ -11143,7 +11140,7 @@
       </c>
       <c r="D86" s="233" t="str">
         <f>D12</f>
-        <v>อาคาร ไอทีเอฟ-ทาวเวอร์ ชั้นที่ 25 เลขที่ 140/61 ถนน สีลม ตำบล/แขวง สุริยวงศ์ อำเภอ/เขต บางรัก จังหวัด กรุงเทพมหานคร 10500</v>
+        <v>เลขที่ 633 ตรอก/ซอย อ่อนนุช30 ตำบล/แขวง ออนนุช อำเภอ/เขต สวนหลวง จังหวัด กรุงเทพมหานคร 10250</v>
       </c>
       <c r="E86" s="233"/>
       <c r="F86" s="233"/>
@@ -11420,7 +11417,7 @@
       <c r="AQ90" s="214"/>
       <c r="AR90" s="214">
         <f>AR16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS90" s="214"/>
       <c r="AT90" s="214">
@@ -11430,29 +11427,29 @@
       <c r="AU90" s="214"/>
       <c r="AV90" s="214">
         <f>AV16</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AW90" s="214"/>
       <c r="AX90" s="214">
         <f>AX16</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY90" s="219"/>
       <c r="AZ90" s="166"/>
       <c r="BA90" s="213">
         <f>BA16</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB90" s="214"/>
       <c r="BC90" s="214">
         <f>BC16</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD90" s="219"/>
       <c r="BE90" s="166"/>
       <c r="BF90" s="216">
         <f>BF16</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BG90" s="217"/>
       <c r="BH90" s="102"/>
@@ -11498,7 +11495,7 @@
       </c>
       <c r="D92" s="234" t="str">
         <f>D18</f>
-        <v>คุณ ณจิตตา วัฒนาภรณ์</v>
+        <v>นาย อภิวัฒน์ บ้านมอญ</v>
       </c>
       <c r="E92" s="234"/>
       <c r="F92" s="234"/>
@@ -11584,7 +11581,7 @@
       </c>
       <c r="D94" s="233" t="str">
         <f>D20</f>
-        <v>400 ซ.บางบอน 5 ซอย 12 แขวงบางบอนเหนือ เขตบางบอน กรุงเทพมหานคร</v>
+        <v>เลขที่ 633 ตรอก/ซอย อ่อนนุช30 ตำบล/แขวง ออนนุช อำเภอ/เขต สวนหลวง จังหวัด กรุงเทพมหานคร 10250</v>
       </c>
       <c r="E94" s="233"/>
       <c r="F94" s="233"/>
@@ -12154,7 +12151,7 @@
       <c r="AR104" s="301"/>
       <c r="AS104" s="302">
         <f>IF(AS30="","",AS30)</f>
-        <v>488100</v>
+        <v>6000</v>
       </c>
       <c r="AT104" s="303"/>
       <c r="AU104" s="303"/>
@@ -12165,7 +12162,7 @@
       <c r="AZ104" s="304"/>
       <c r="BA104" s="296">
         <f>+BA30</f>
-        <v>12567.33</v>
+        <v>0</v>
       </c>
       <c r="BB104" s="297"/>
       <c r="BC104" s="297"/>
@@ -14038,7 +14035,7 @@
       <c r="AR128" s="135"/>
       <c r="AS128" s="188">
         <f>SUM(AS104:AS126)</f>
-        <v>488100</v>
+        <v>6000</v>
       </c>
       <c r="AT128" s="189"/>
       <c r="AU128" s="189"/>
@@ -14290,7 +14287,7 @@
       </c>
       <c r="AM132" s="260">
         <f>+AM58</f>
-        <v>9000</v>
+        <v>750</v>
       </c>
       <c r="AN132" s="260"/>
       <c r="AO132" s="260"/>

--- a/Excel_pnd1k/excel_data_pnd1k.xlsx
+++ b/Excel_pnd1k/excel_data_pnd1k.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6becf00b5c44c692/เอกสาร/GitHub/Bot_Server/Excel_pnd1k/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3335" documentId="8_{E62BB257-A0A0-4383-8146-1EEB7D39A510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E71723C-E567-43DA-9CEB-AA80FF0638C0}"/>
+  <xr:revisionPtr revIDLastSave="3495" documentId="8_{E62BB257-A0A0-4383-8146-1EEB7D39A510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BC4D68A-4FAB-46A8-B70E-4C53F6E2D851}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="134">
   <si>
     <t>ชื่อ</t>
   </si>
@@ -578,16 +578,19 @@
     <t>31/12/2025</t>
   </si>
   <si>
-    <t>บริษัท เน็กซ์สเต็ป แมเนจเม้นท์ จำกัด รายเดือน</t>
+    <t>บริษัท แอมมิรี ไร้ขีด จำกัด</t>
   </si>
   <si>
-    <t>เลขที่ 633 ตรอก/ซอย อ่อนนุช30 ตำบล/แขวง ออนนุช อำเภอ/เขต สวนหลวง จังหวัด กรุงเทพมหานคร 10250</t>
+    <t>เลขที่8/36 หมู่ที่ 1 ตำบล/แขวง เนินพระ อำเภอ/เขต เมืองระยอง จังหวัด ระยอง รหัสไปรษณีย์ 21000</t>
+  </si>
+  <si>
+    <t>เลขที่ 5/148 หมู่ที่ 2 ตำบลเชิงเนิน อำเภอเมืองระยอง จังหวัดระยอง</t>
   </si>
   <si>
     <t>ศูนย์บาทถ้วน</t>
   </si>
   <si>
-    <t>นาย อภิวัฒน์ บ้านมอญ</t>
+    <t>นาย สุชญา สุขวิบูลย์</t>
   </si>
 </sst>
 </file>
@@ -6889,11 +6892,11 @@
       <c r="AE8" s="217"/>
       <c r="AF8" s="166"/>
       <c r="AG8" s="213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="214"/>
       <c r="AI8" s="214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="214"/>
       <c r="AK8" s="214">
@@ -6910,7 +6913,7 @@
       </c>
       <c r="AQ8" s="214"/>
       <c r="AR8" s="214">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS8" s="214"/>
       <c r="AT8" s="214">
@@ -6918,16 +6921,16 @@
       </c>
       <c r="AU8" s="214"/>
       <c r="AV8" s="214">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW8" s="214"/>
       <c r="AX8" s="214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY8" s="219"/>
       <c r="AZ8" s="166"/>
       <c r="BA8" s="213">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB8" s="214"/>
       <c r="BC8" s="214">
@@ -6936,7 +6939,7 @@
       <c r="BD8" s="219"/>
       <c r="BE8" s="166"/>
       <c r="BF8" s="216">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BG8" s="217"/>
       <c r="BH8" s="102"/>
@@ -7310,7 +7313,7 @@
         <v>59</v>
       </c>
       <c r="AD16" s="216">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" s="217"/>
       <c r="AF16" s="166"/>
@@ -7323,11 +7326,11 @@
       </c>
       <c r="AJ16" s="214"/>
       <c r="AK16" s="214">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="214"/>
       <c r="AM16" s="214">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN16" s="219"/>
       <c r="AO16" s="166"/>
@@ -7336,33 +7339,33 @@
       </c>
       <c r="AQ16" s="214"/>
       <c r="AR16" s="214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS16" s="214"/>
       <c r="AT16" s="214">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" s="214"/>
       <c r="AV16" s="214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW16" s="214"/>
       <c r="AX16" s="214">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY16" s="219"/>
       <c r="AZ16" s="166"/>
       <c r="BA16" s="213">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB16" s="214"/>
       <c r="BC16" s="214">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BD16" s="219"/>
       <c r="BE16" s="166"/>
       <c r="BF16" s="216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BG16" s="217"/>
       <c r="BH16" s="102"/>
@@ -7414,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="234" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18" s="234"/>
       <c r="F18" s="234"/>
@@ -7499,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="232" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="233"/>
       <c r="F20" s="233"/>
@@ -8104,7 +8107,7 @@
       <c r="AQ30" s="300"/>
       <c r="AR30" s="301"/>
       <c r="AS30" s="326">
-        <v>6000</v>
+        <v>200000</v>
       </c>
       <c r="AT30" s="327"/>
       <c r="AU30" s="327"/>
@@ -8166,7 +8169,9 @@
       <c r="AH31" s="93"/>
       <c r="AI31" s="93"/>
       <c r="AJ31" s="93"/>
-      <c r="AK31" s="199"/>
+      <c r="AK31" s="199" t="s">
+        <v>128</v>
+      </c>
       <c r="AL31" s="200"/>
       <c r="AM31" s="200"/>
       <c r="AN31" s="200"/>
@@ -8174,7 +8179,9 @@
       <c r="AP31" s="200"/>
       <c r="AQ31" s="200"/>
       <c r="AR31" s="201"/>
-      <c r="AS31" s="180"/>
+      <c r="AS31" s="180">
+        <v>340000</v>
+      </c>
       <c r="AT31" s="181"/>
       <c r="AU31" s="181"/>
       <c r="AV31" s="181"/>
@@ -8182,7 +8189,9 @@
       <c r="AX31" s="181"/>
       <c r="AY31" s="181"/>
       <c r="AZ31" s="182"/>
-      <c r="BA31" s="170"/>
+      <c r="BA31" s="170">
+        <v>0</v>
+      </c>
       <c r="BB31" s="171"/>
       <c r="BC31" s="172"/>
       <c r="BD31" s="172"/>
@@ -9656,7 +9665,7 @@
       </c>
       <c r="AR54" s="135"/>
       <c r="AS54" s="188">
-        <v>6000</v>
+        <v>200000</v>
       </c>
       <c r="AT54" s="189"/>
       <c r="AU54" s="189"/>
@@ -9746,7 +9755,7 @@
         <v>37</v>
       </c>
       <c r="P56" s="261" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q56" s="262"/>
       <c r="R56" s="262"/>
@@ -9905,7 +9914,7 @@
         <v>75</v>
       </c>
       <c r="AM58" s="330">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="AN58" s="330"/>
       <c r="AO58" s="330"/>
@@ -10950,12 +10959,12 @@
       <c r="AF82" s="166"/>
       <c r="AG82" s="213">
         <f>AG8</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH82" s="214"/>
       <c r="AI82" s="214">
         <f>AI8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ82" s="214"/>
       <c r="AK82" s="214">
@@ -10976,7 +10985,7 @@
       <c r="AQ82" s="214"/>
       <c r="AR82" s="214">
         <f>AR8</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS82" s="214"/>
       <c r="AT82" s="214">
@@ -10986,18 +10995,18 @@
       <c r="AU82" s="214"/>
       <c r="AV82" s="214">
         <f>AV8</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW82" s="214"/>
       <c r="AX82" s="214">
         <f>AX8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY82" s="219"/>
       <c r="AZ82" s="166"/>
       <c r="BA82" s="213">
         <f>BA8</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB82" s="214"/>
       <c r="BC82" s="214">
@@ -11008,7 +11017,7 @@
       <c r="BE82" s="166"/>
       <c r="BF82" s="216">
         <f>BF8</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BG82" s="217"/>
       <c r="BH82" s="102"/>
@@ -11054,7 +11063,7 @@
       </c>
       <c r="D84" s="235" t="str">
         <f>D10</f>
-        <v>บริษัท เน็กซ์สเต็ป แมเนจเม้นท์ จำกัด รายเดือน</v>
+        <v>บริษัท แอมมิรี ไร้ขีด จำกัด</v>
       </c>
       <c r="E84" s="235"/>
       <c r="F84" s="235"/>
@@ -11140,7 +11149,7 @@
       </c>
       <c r="D86" s="233" t="str">
         <f>D12</f>
-        <v>เลขที่ 633 ตรอก/ซอย อ่อนนุช30 ตำบล/แขวง ออนนุช อำเภอ/เขต สวนหลวง จังหวัด กรุงเทพมหานคร 10250</v>
+        <v>เลขที่8/36 หมู่ที่ 1 ตำบล/แขวง เนินพระ อำเภอ/เขต เมืองระยอง จังหวัด ระยอง รหัสไปรษณีย์ 21000</v>
       </c>
       <c r="E86" s="233"/>
       <c r="F86" s="233"/>
@@ -11385,7 +11394,7 @@
       </c>
       <c r="AD90" s="216">
         <f>AD16</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE90" s="217"/>
       <c r="AF90" s="166"/>
@@ -11401,12 +11410,12 @@
       <c r="AJ90" s="214"/>
       <c r="AK90" s="214">
         <f>AK16</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL90" s="214"/>
       <c r="AM90" s="214">
         <f>AM16</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN90" s="219"/>
       <c r="AO90" s="166"/>
@@ -11417,39 +11426,39 @@
       <c r="AQ90" s="214"/>
       <c r="AR90" s="214">
         <f>AR16</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS90" s="214"/>
       <c r="AT90" s="214">
         <f>AT16</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU90" s="214"/>
       <c r="AV90" s="214">
         <f>AV16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW90" s="214"/>
       <c r="AX90" s="214">
         <f>AX16</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY90" s="219"/>
       <c r="AZ90" s="166"/>
       <c r="BA90" s="213">
         <f>BA16</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB90" s="214"/>
       <c r="BC90" s="214">
         <f>BC16</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BD90" s="219"/>
       <c r="BE90" s="166"/>
       <c r="BF90" s="216">
         <f>BF16</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BG90" s="217"/>
       <c r="BH90" s="102"/>
@@ -11495,7 +11504,7 @@
       </c>
       <c r="D92" s="234" t="str">
         <f>D18</f>
-        <v>นาย อภิวัฒน์ บ้านมอญ</v>
+        <v>นาย สุชญา สุขวิบูลย์</v>
       </c>
       <c r="E92" s="234"/>
       <c r="F92" s="234"/>
@@ -11581,7 +11590,7 @@
       </c>
       <c r="D94" s="233" t="str">
         <f>D20</f>
-        <v>เลขที่ 633 ตรอก/ซอย อ่อนนุช30 ตำบล/แขวง ออนนุช อำเภอ/เขต สวนหลวง จังหวัด กรุงเทพมหานคร 10250</v>
+        <v>เลขที่ 5/148 หมู่ที่ 2 ตำบลเชิงเนิน อำเภอเมืองระยอง จังหวัดระยอง</v>
       </c>
       <c r="E94" s="233"/>
       <c r="F94" s="233"/>
@@ -12151,7 +12160,7 @@
       <c r="AR104" s="301"/>
       <c r="AS104" s="302">
         <f>IF(AS30="","",AS30)</f>
-        <v>6000</v>
+        <v>200000</v>
       </c>
       <c r="AT104" s="303"/>
       <c r="AU104" s="303"/>
@@ -12216,7 +12225,7 @@
       <c r="AJ105" s="93"/>
       <c r="AK105" s="244" t="str">
         <f>IF(AK31="","",AK31)</f>
-        <v/>
+        <v>31/12/2025</v>
       </c>
       <c r="AL105" s="245"/>
       <c r="AM105" s="245"/>
@@ -12225,9 +12234,9 @@
       <c r="AP105" s="245"/>
       <c r="AQ105" s="245"/>
       <c r="AR105" s="246"/>
-      <c r="AS105" s="264" t="str">
+      <c r="AS105" s="264">
         <f>IF(AS31="","",AS31)</f>
-        <v/>
+        <v>340000</v>
       </c>
       <c r="AT105" s="265"/>
       <c r="AU105" s="265"/>
@@ -12236,9 +12245,9 @@
       <c r="AX105" s="265"/>
       <c r="AY105" s="265"/>
       <c r="AZ105" s="276"/>
-      <c r="BA105" s="193" t="str">
+      <c r="BA105" s="193">
         <f>IF(BA31="","",BA31)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB105" s="194"/>
       <c r="BC105" s="191" t="str">
@@ -14035,7 +14044,7 @@
       <c r="AR128" s="135"/>
       <c r="AS128" s="188">
         <f>SUM(AS104:AS126)</f>
-        <v>6000</v>
+        <v>540000</v>
       </c>
       <c r="AT128" s="189"/>
       <c r="AU128" s="189"/>
@@ -14287,7 +14296,7 @@
       </c>
       <c r="AM132" s="260">
         <f>+AM58</f>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="AN132" s="260"/>
       <c r="AO132" s="260"/>

--- a/Excel_pnd1k/excel_data_pnd1k.xlsx
+++ b/Excel_pnd1k/excel_data_pnd1k.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6becf00b5c44c692/เอกสาร/GitHub/Bot_Server/Excel_pnd1k/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\github\Bot_Server\Excel_pnd1k\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1388" documentId="6_{DC7EFBB4-F84A-4393-88C7-A29FB3FBFE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AB26EC4-4814-44CE-ABFF-858F0A3FDDE7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE438775-E368-4096-903A-CF846D3284D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="14010" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="5" state="hidden" r:id="rId1"/>
@@ -1977,7 +1977,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="353">
+  <cellXfs count="356">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -2908,9 +2908,6 @@
     <xf numFmtId="43" fontId="26" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="85" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="26" fillId="0" borderId="88" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2930,15 +2927,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2993,6 +2981,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="45" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="46" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="65" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="85" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5655,8 +5664,8 @@
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>123825</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>732</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5711,10 +5720,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6210,11 +6215,11 @@
     </row>
     <row r="3" spans="1:31" ht="23.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="53"/>
-      <c r="B3" s="343" t="s">
+      <c r="B3" s="339" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="344"/>
-      <c r="D3" s="345"/>
+      <c r="C3" s="340"/>
+      <c r="D3" s="341"/>
       <c r="E3" s="58"/>
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
@@ -6326,8 +6331,8 @@
       <c r="G5" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="339"/>
-      <c r="I5" s="340"/>
+      <c r="H5" s="335"/>
+      <c r="I5" s="336"/>
       <c r="J5" s="50"/>
     </row>
     <row r="6" spans="1:31" s="12" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -6347,10 +6352,10 @@
       <c r="B7" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="346"/>
-      <c r="D7" s="347"/>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+      <c r="C7" s="342"/>
+      <c r="D7" s="343"/>
+      <c r="E7" s="343"/>
+      <c r="F7" s="343"/>
       <c r="G7" s="19" t="s">
         <v>112</v>
       </c>
@@ -6368,9 +6373,9 @@
         <v>115</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="348"/>
-      <c r="E8" s="349"/>
-      <c r="F8" s="350"/>
+      <c r="D8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="346"/>
       <c r="G8" s="86"/>
       <c r="H8" s="87"/>
       <c r="I8" s="91">
@@ -6385,9 +6390,9 @@
         <v>116</v>
       </c>
       <c r="C9" s="23"/>
-      <c r="D9" s="351"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
+      <c r="D9" s="347"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="G9" s="88"/>
       <c r="H9" s="89"/>
       <c r="I9" s="92">
@@ -6428,8 +6433,8 @@
         <v>106</v>
       </c>
       <c r="C12" s="25"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="342"/>
+      <c r="D12" s="337"/>
+      <c r="E12" s="338"/>
       <c r="F12" s="49"/>
       <c r="G12" s="49"/>
       <c r="H12" s="49"/>
@@ -8099,22 +8104,22 @@
       <c r="AP30" s="300"/>
       <c r="AQ30" s="300"/>
       <c r="AR30" s="301"/>
-      <c r="AS30" s="326"/>
-      <c r="AT30" s="327"/>
-      <c r="AU30" s="327"/>
-      <c r="AV30" s="327"/>
-      <c r="AW30" s="327"/>
-      <c r="AX30" s="327"/>
-      <c r="AY30" s="327"/>
-      <c r="AZ30" s="328"/>
-      <c r="BA30" s="336"/>
-      <c r="BB30" s="337"/>
-      <c r="BC30" s="337"/>
-      <c r="BD30" s="337"/>
-      <c r="BE30" s="337"/>
-      <c r="BF30" s="337"/>
-      <c r="BG30" s="337"/>
-      <c r="BH30" s="338"/>
+      <c r="AS30" s="353"/>
+      <c r="AT30" s="354"/>
+      <c r="AU30" s="354"/>
+      <c r="AV30" s="354"/>
+      <c r="AW30" s="354"/>
+      <c r="AX30" s="354"/>
+      <c r="AY30" s="354"/>
+      <c r="AZ30" s="355"/>
+      <c r="BA30" s="326"/>
+      <c r="BB30" s="327"/>
+      <c r="BC30" s="327"/>
+      <c r="BD30" s="327"/>
+      <c r="BE30" s="327"/>
+      <c r="BF30" s="327"/>
+      <c r="BG30" s="327"/>
+      <c r="BH30" s="349"/>
       <c r="BI30" s="102"/>
     </row>
     <row r="31" spans="1:70" ht="15.95" customHeight="1" x14ac:dyDescent="0.5">
@@ -8178,16 +8183,16 @@
       <c r="AX31" s="181"/>
       <c r="AY31" s="181"/>
       <c r="AZ31" s="182"/>
-      <c r="BA31" s="170">
+      <c r="BA31" s="350">
         <v>290.76</v>
       </c>
-      <c r="BB31" s="171"/>
-      <c r="BC31" s="172"/>
-      <c r="BD31" s="172"/>
-      <c r="BE31" s="172"/>
-      <c r="BF31" s="172"/>
-      <c r="BG31" s="172"/>
-      <c r="BH31" s="173"/>
+      <c r="BB31" s="351"/>
+      <c r="BC31" s="351"/>
+      <c r="BD31" s="351"/>
+      <c r="BE31" s="351"/>
+      <c r="BF31" s="351"/>
+      <c r="BG31" s="351"/>
+      <c r="BH31" s="352"/>
       <c r="BI31" s="102"/>
     </row>
     <row r="32" spans="1:70" ht="15.95" customHeight="1" x14ac:dyDescent="0.5">
@@ -8562,14 +8567,14 @@
       <c r="AH37" s="93"/>
       <c r="AI37" s="93"/>
       <c r="AJ37" s="93"/>
-      <c r="AK37" s="331"/>
-      <c r="AL37" s="332"/>
-      <c r="AM37" s="332"/>
-      <c r="AN37" s="332"/>
-      <c r="AO37" s="332"/>
-      <c r="AP37" s="332"/>
-      <c r="AQ37" s="332"/>
-      <c r="AR37" s="333"/>
+      <c r="AK37" s="330"/>
+      <c r="AL37" s="331"/>
+      <c r="AM37" s="331"/>
+      <c r="AN37" s="331"/>
+      <c r="AO37" s="331"/>
+      <c r="AP37" s="331"/>
+      <c r="AQ37" s="331"/>
+      <c r="AR37" s="332"/>
       <c r="AS37" s="316"/>
       <c r="AT37" s="317"/>
       <c r="AU37" s="317"/>
@@ -8883,14 +8888,14 @@
       <c r="AH42" s="93"/>
       <c r="AI42" s="93"/>
       <c r="AJ42" s="93"/>
-      <c r="AK42" s="331"/>
-      <c r="AL42" s="332"/>
-      <c r="AM42" s="332"/>
-      <c r="AN42" s="332"/>
-      <c r="AO42" s="332"/>
-      <c r="AP42" s="332"/>
-      <c r="AQ42" s="332"/>
-      <c r="AR42" s="333"/>
+      <c r="AK42" s="330"/>
+      <c r="AL42" s="331"/>
+      <c r="AM42" s="331"/>
+      <c r="AN42" s="331"/>
+      <c r="AO42" s="331"/>
+      <c r="AP42" s="331"/>
+      <c r="AQ42" s="331"/>
+      <c r="AR42" s="332"/>
       <c r="AS42" s="316"/>
       <c r="AT42" s="317"/>
       <c r="AU42" s="317"/>
@@ -9011,14 +9016,14 @@
       <c r="AH44" s="93"/>
       <c r="AI44" s="93"/>
       <c r="AJ44" s="93"/>
-      <c r="AK44" s="331"/>
-      <c r="AL44" s="332"/>
-      <c r="AM44" s="332"/>
-      <c r="AN44" s="332"/>
-      <c r="AO44" s="332"/>
-      <c r="AP44" s="332"/>
-      <c r="AQ44" s="332"/>
-      <c r="AR44" s="333"/>
+      <c r="AK44" s="330"/>
+      <c r="AL44" s="331"/>
+      <c r="AM44" s="331"/>
+      <c r="AN44" s="331"/>
+      <c r="AO44" s="331"/>
+      <c r="AP44" s="331"/>
+      <c r="AQ44" s="331"/>
+      <c r="AR44" s="332"/>
       <c r="AS44" s="316"/>
       <c r="AT44" s="317"/>
       <c r="AU44" s="317"/>
@@ -9533,21 +9538,21 @@
       <c r="AG52" s="254"/>
       <c r="AH52" s="254"/>
       <c r="AI52" s="254"/>
-      <c r="AK52" s="331"/>
-      <c r="AL52" s="332"/>
-      <c r="AM52" s="332"/>
-      <c r="AN52" s="332"/>
-      <c r="AO52" s="332"/>
-      <c r="AP52" s="332"/>
-      <c r="AQ52" s="332"/>
-      <c r="AR52" s="333"/>
-      <c r="AS52" s="329"/>
-      <c r="AT52" s="329"/>
-      <c r="AU52" s="329"/>
-      <c r="AV52" s="329"/>
-      <c r="AW52" s="329"/>
-      <c r="AX52" s="329"/>
-      <c r="AY52" s="329"/>
+      <c r="AK52" s="330"/>
+      <c r="AL52" s="331"/>
+      <c r="AM52" s="331"/>
+      <c r="AN52" s="331"/>
+      <c r="AO52" s="331"/>
+      <c r="AP52" s="331"/>
+      <c r="AQ52" s="331"/>
+      <c r="AR52" s="332"/>
+      <c r="AS52" s="328"/>
+      <c r="AT52" s="328"/>
+      <c r="AU52" s="328"/>
+      <c r="AV52" s="328"/>
+      <c r="AW52" s="328"/>
+      <c r="AX52" s="328"/>
+      <c r="AY52" s="328"/>
       <c r="AZ52" s="180"/>
       <c r="BA52" s="225"/>
       <c r="BB52" s="226"/>
@@ -9902,12 +9907,12 @@
       <c r="AL58" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="AM58" s="330">
+      <c r="AM58" s="329">
         <v>0</v>
       </c>
-      <c r="AN58" s="330"/>
-      <c r="AO58" s="330"/>
-      <c r="AP58" s="330"/>
+      <c r="AN58" s="329"/>
+      <c r="AO58" s="329"/>
+      <c r="AP58" s="329"/>
       <c r="AQ58" s="139" t="s">
         <v>74</v>
       </c>
@@ -10446,19 +10451,19 @@
       <c r="AE68" s="93"/>
       <c r="AF68" s="93"/>
       <c r="AG68" s="93"/>
-      <c r="AI68" s="335" t="s">
+      <c r="AI68" s="334" t="s">
         <v>54</v>
       </c>
-      <c r="AJ68" s="335"/>
-      <c r="AK68" s="335"/>
-      <c r="AL68" s="335"/>
-      <c r="AM68" s="335"/>
-      <c r="AN68" s="335"/>
-      <c r="AO68" s="335"/>
-      <c r="AP68" s="335"/>
-      <c r="AQ68" s="335"/>
-      <c r="AR68" s="335"/>
-      <c r="AS68" s="335"/>
+      <c r="AJ68" s="334"/>
+      <c r="AK68" s="334"/>
+      <c r="AL68" s="334"/>
+      <c r="AM68" s="334"/>
+      <c r="AN68" s="334"/>
+      <c r="AO68" s="334"/>
+      <c r="AP68" s="334"/>
+      <c r="AQ68" s="334"/>
+      <c r="AR68" s="334"/>
+      <c r="AS68" s="334"/>
       <c r="AT68" s="93"/>
       <c r="AU68" s="93"/>
       <c r="AV68" s="93"/>
@@ -14741,22 +14746,22 @@
       <c r="T140" s="161"/>
       <c r="Z140" s="159"/>
       <c r="AF140" s="108"/>
-      <c r="AG140" s="334"/>
-      <c r="AH140" s="334"/>
-      <c r="AI140" s="334"/>
-      <c r="AJ140" s="334"/>
-      <c r="AK140" s="334"/>
-      <c r="AL140" s="334"/>
-      <c r="AM140" s="334"/>
-      <c r="AN140" s="334"/>
-      <c r="AO140" s="334"/>
-      <c r="AP140" s="334"/>
-      <c r="AQ140" s="334"/>
-      <c r="AR140" s="334"/>
-      <c r="AS140" s="334"/>
-      <c r="AT140" s="334"/>
-      <c r="AU140" s="334"/>
-      <c r="AV140" s="334"/>
+      <c r="AG140" s="333"/>
+      <c r="AH140" s="333"/>
+      <c r="AI140" s="333"/>
+      <c r="AJ140" s="333"/>
+      <c r="AK140" s="333"/>
+      <c r="AL140" s="333"/>
+      <c r="AM140" s="333"/>
+      <c r="AN140" s="333"/>
+      <c r="AO140" s="333"/>
+      <c r="AP140" s="333"/>
+      <c r="AQ140" s="333"/>
+      <c r="AR140" s="333"/>
+      <c r="AS140" s="333"/>
+      <c r="AT140" s="333"/>
+      <c r="AU140" s="333"/>
+      <c r="AV140" s="333"/>
       <c r="BH140" s="102"/>
       <c r="BI140" s="102"/>
     </row>
@@ -15057,7 +15062,7 @@
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="404">
+  <mergeCells count="403">
     <mergeCell ref="BA106:BB106"/>
     <mergeCell ref="BA90:BB90"/>
     <mergeCell ref="BC90:BD90"/>
@@ -15382,14 +15387,13 @@
     <mergeCell ref="Y23:AF23"/>
     <mergeCell ref="AK18:AL18"/>
     <mergeCell ref="BC35:BH35"/>
-    <mergeCell ref="BA31:BB31"/>
     <mergeCell ref="AS33:AZ33"/>
-    <mergeCell ref="BC31:BH31"/>
     <mergeCell ref="BA33:BB33"/>
     <mergeCell ref="AW18:AX18"/>
     <mergeCell ref="AY18:AZ18"/>
     <mergeCell ref="AR23:AY23"/>
     <mergeCell ref="BA34:BB34"/>
+    <mergeCell ref="BA31:BH31"/>
     <mergeCell ref="BY4:CB4"/>
     <mergeCell ref="BY5:CF5"/>
     <mergeCell ref="B6:BH6"/>

--- a/Excel_pnd1k/excel_data_pnd1k.xlsx
+++ b/Excel_pnd1k/excel_data_pnd1k.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6becf00b5c44c692/เอกสาร/GitHub/Bot_Server/Excel_pnd1k/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11687" documentId="6_{DC7EFBB4-F84A-4393-88C7-A29FB3FBFE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC697156-596B-402E-BD9A-2AC150C218B2}"/>
+  <xr:revisionPtr revIDLastSave="12721" documentId="6_{DC7EFBB4-F84A-4393-88C7-A29FB3FBFE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15ADEBAD-6CAC-4744-960D-92018C86AF79}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3705" yWindow="2445" windowWidth="21600" windowHeight="11295" tabRatio="631" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="5" state="hidden" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="134">
   <si>
     <t>ชื่อ</t>
   </si>
@@ -578,16 +578,19 @@
     <t>31/12/2025</t>
   </si>
   <si>
-    <t>บริษัท อ่างทองเคเบิลทีวี จำกัด</t>
+    <t>บริษัท อัลฟ่า ซัพพลาย จำกัด</t>
   </si>
   <si>
-    <t>เลขที่ 18/2 ถนนอ่างทอง-สิงห์บุรี ตำบลตลาดหลวง อำเภอเมืองอ่างทอง จังหวัดอ่างทอง 14000</t>
+    <t>อาคาร - ห้องเลขที่ - ชั้นที่ - หมู่บ้าน - เลขที่ 35/3 หมู่ที่ 5 ถนน - ตำบลคอกกระบือ อำเภอเมืองสมุทรสาคร จังหวัดสมุทรสาคร 74000</t>
   </si>
   <si>
-    <t>นาย สงกรานต์ กลิ่นดอกไม้</t>
+    <t>ศูนย์บาทถ้วน</t>
   </si>
   <si>
-    <t>หนึ่งร้อยแปดสิบแปดบาทสิบห้าสตางค์</t>
+    <t>นางสาว ภริตพร ขำต้นวงศ์</t>
+  </si>
+  <si>
+    <t>989 ซ.เพรชเกษม 79 หนองแขม หนองแขม กรุงเทพมหานคร 10160</t>
   </si>
 </sst>
 </file>
@@ -2985,14 +2988,20 @@
     <xf numFmtId="43" fontId="26" fillId="0" borderId="35" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="192" fontId="26" fillId="0" borderId="77" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="26" fillId="0" borderId="78" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="26" fillId="0" borderId="45" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="192" fontId="26" fillId="0" borderId="77" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="192" fontId="26" fillId="0" borderId="78" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="46" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="65" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3067,12 +3076,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="26" fillId="0" borderId="46" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="26" fillId="0" borderId="65" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6290,11 +6293,11 @@
     </row>
     <row r="3" spans="1:31" ht="23.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="53"/>
-      <c r="B3" s="351" t="s">
+      <c r="B3" s="353" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="352"/>
-      <c r="D3" s="353"/>
+      <c r="C3" s="354"/>
+      <c r="D3" s="355"/>
       <c r="E3" s="58"/>
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
@@ -6406,8 +6409,8 @@
       <c r="G5" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="347"/>
-      <c r="I5" s="348"/>
+      <c r="H5" s="349"/>
+      <c r="I5" s="350"/>
       <c r="J5" s="50"/>
     </row>
     <row r="6" spans="1:31" s="12" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -6427,10 +6430,10 @@
       <c r="B7" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="354"/>
-      <c r="D7" s="355"/>
-      <c r="E7" s="355"/>
-      <c r="F7" s="355"/>
+      <c r="C7" s="356"/>
+      <c r="D7" s="357"/>
+      <c r="E7" s="357"/>
+      <c r="F7" s="357"/>
       <c r="G7" s="19" t="s">
         <v>112</v>
       </c>
@@ -6448,9 +6451,9 @@
         <v>115</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="356"/>
-      <c r="E8" s="357"/>
-      <c r="F8" s="358"/>
+      <c r="D8" s="358"/>
+      <c r="E8" s="359"/>
+      <c r="F8" s="360"/>
       <c r="G8" s="86"/>
       <c r="H8" s="87"/>
       <c r="I8" s="91">
@@ -6465,9 +6468,9 @@
         <v>116</v>
       </c>
       <c r="C9" s="23"/>
-      <c r="D9" s="359"/>
-      <c r="E9" s="360"/>
-      <c r="F9" s="360"/>
+      <c r="D9" s="361"/>
+      <c r="E9" s="362"/>
+      <c r="F9" s="362"/>
       <c r="G9" s="88"/>
       <c r="H9" s="89"/>
       <c r="I9" s="92">
@@ -6508,8 +6511,8 @@
         <v>106</v>
       </c>
       <c r="C12" s="25"/>
-      <c r="D12" s="349"/>
-      <c r="E12" s="350"/>
+      <c r="D12" s="351"/>
+      <c r="E12" s="352"/>
       <c r="F12" s="49"/>
       <c r="G12" s="49"/>
       <c r="H12" s="49"/>
@@ -6748,12 +6751,12 @@
       <c r="BX4" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="BY4" s="341">
+      <c r="BY4" s="343">
         <v>2022</v>
       </c>
-      <c r="BZ4" s="341"/>
-      <c r="CA4" s="341"/>
-      <c r="CB4" s="341"/>
+      <c r="BZ4" s="343"/>
+      <c r="CA4" s="343"/>
+      <c r="CB4" s="343"/>
     </row>
     <row r="5" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="98"/>
@@ -6804,12 +6807,12 @@
       <c r="AZ5" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="BC5" s="343"/>
-      <c r="BD5" s="343"/>
-      <c r="BE5" s="343"/>
-      <c r="BF5" s="343"/>
-      <c r="BG5" s="343"/>
-      <c r="BH5" s="343"/>
+      <c r="BC5" s="345"/>
+      <c r="BD5" s="345"/>
+      <c r="BE5" s="345"/>
+      <c r="BF5" s="345"/>
+      <c r="BG5" s="345"/>
+      <c r="BH5" s="345"/>
       <c r="BI5" s="102"/>
       <c r="BT5" s="93" t="s">
         <v>85</v>
@@ -6817,16 +6820,16 @@
       <c r="BX5" s="99" t="s">
         <v>97</v>
       </c>
-      <c r="BY5" s="342" t="s">
+      <c r="BY5" s="344" t="s">
         <v>99</v>
       </c>
-      <c r="BZ5" s="342"/>
-      <c r="CA5" s="342"/>
-      <c r="CB5" s="342"/>
-      <c r="CC5" s="342"/>
-      <c r="CD5" s="342"/>
-      <c r="CE5" s="342"/>
-      <c r="CF5" s="342"/>
+      <c r="BZ5" s="344"/>
+      <c r="CA5" s="344"/>
+      <c r="CB5" s="344"/>
+      <c r="CC5" s="344"/>
+      <c r="CD5" s="344"/>
+      <c r="CE5" s="344"/>
+      <c r="CF5" s="344"/>
     </row>
     <row r="6" spans="1:84" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="98"/>
@@ -6969,11 +6972,11 @@
       <c r="AE8" s="227"/>
       <c r="AF8" s="166"/>
       <c r="AG8" s="172">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH8" s="173"/>
       <c r="AI8" s="173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" s="173"/>
       <c r="AK8" s="173">
@@ -6986,11 +6989,11 @@
       <c r="AN8" s="174"/>
       <c r="AO8" s="166"/>
       <c r="AP8" s="172">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ8" s="173"/>
       <c r="AR8" s="173">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS8" s="173"/>
       <c r="AT8" s="173">
@@ -7002,21 +7005,21 @@
       </c>
       <c r="AW8" s="173"/>
       <c r="AX8" s="173">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY8" s="174"/>
       <c r="AZ8" s="166"/>
       <c r="BA8" s="172">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB8" s="173"/>
       <c r="BC8" s="173">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="174"/>
       <c r="BE8" s="166"/>
       <c r="BF8" s="226">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BG8" s="227"/>
       <c r="BH8" s="102"/>
@@ -7395,19 +7398,19 @@
       <c r="AE16" s="227"/>
       <c r="AF16" s="166"/>
       <c r="AG16" s="172">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH16" s="173"/>
       <c r="AI16" s="173">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AJ16" s="173"/>
       <c r="AK16" s="173">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL16" s="173"/>
       <c r="AM16" s="173">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN16" s="174"/>
       <c r="AO16" s="166"/>
@@ -7420,11 +7423,11 @@
       </c>
       <c r="AS16" s="173"/>
       <c r="AT16" s="173">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" s="173"/>
       <c r="AV16" s="173">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AW16" s="173"/>
       <c r="AX16" s="173">
@@ -7433,16 +7436,16 @@
       <c r="AY16" s="174"/>
       <c r="AZ16" s="166"/>
       <c r="BA16" s="172">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BB16" s="173"/>
       <c r="BC16" s="173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD16" s="174"/>
       <c r="BE16" s="166"/>
       <c r="BF16" s="226">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BG16" s="227"/>
       <c r="BH16" s="102"/>
@@ -7494,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="231" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18" s="231"/>
       <c r="F18" s="231"/>
@@ -7579,7 +7582,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="335" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E20" s="276"/>
       <c r="F20" s="276"/>
@@ -8173,7 +8176,9 @@
       <c r="AH30" s="93"/>
       <c r="AI30" s="93"/>
       <c r="AJ30" s="93"/>
-      <c r="AK30" s="256"/>
+      <c r="AK30" s="256" t="s">
+        <v>128</v>
+      </c>
       <c r="AL30" s="257"/>
       <c r="AM30" s="257"/>
       <c r="AN30" s="257"/>
@@ -8181,7 +8186,9 @@
       <c r="AP30" s="257"/>
       <c r="AQ30" s="257"/>
       <c r="AR30" s="258"/>
-      <c r="AS30" s="266"/>
+      <c r="AS30" s="266">
+        <v>4976</v>
+      </c>
       <c r="AT30" s="267"/>
       <c r="AU30" s="267"/>
       <c r="AV30" s="267"/>
@@ -8189,7 +8196,9 @@
       <c r="AX30" s="267"/>
       <c r="AY30" s="267"/>
       <c r="AZ30" s="268"/>
-      <c r="BA30" s="177"/>
+      <c r="BA30" s="177">
+        <v>0</v>
+      </c>
       <c r="BB30" s="178"/>
       <c r="BC30" s="178"/>
       <c r="BD30" s="178"/>
@@ -8240,9 +8249,7 @@
       <c r="AH31" s="93"/>
       <c r="AI31" s="93"/>
       <c r="AJ31" s="93"/>
-      <c r="AK31" s="190" t="s">
-        <v>128</v>
-      </c>
+      <c r="AK31" s="190"/>
       <c r="AL31" s="191"/>
       <c r="AM31" s="191"/>
       <c r="AN31" s="191"/>
@@ -8250,9 +8257,7 @@
       <c r="AP31" s="191"/>
       <c r="AQ31" s="191"/>
       <c r="AR31" s="192"/>
-      <c r="AS31" s="205">
-        <v>6271.56</v>
-      </c>
+      <c r="AS31" s="205"/>
       <c r="AT31" s="206"/>
       <c r="AU31" s="206"/>
       <c r="AV31" s="206"/>
@@ -8260,16 +8265,14 @@
       <c r="AX31" s="206"/>
       <c r="AY31" s="206"/>
       <c r="AZ31" s="207"/>
-      <c r="BA31" s="338">
-        <v>188.15</v>
-      </c>
-      <c r="BB31" s="361"/>
-      <c r="BC31" s="361"/>
-      <c r="BD31" s="361"/>
-      <c r="BE31" s="361"/>
-      <c r="BF31" s="361"/>
-      <c r="BG31" s="361"/>
-      <c r="BH31" s="362"/>
+      <c r="BA31" s="340"/>
+      <c r="BB31" s="341"/>
+      <c r="BC31" s="341"/>
+      <c r="BD31" s="341"/>
+      <c r="BE31" s="341"/>
+      <c r="BF31" s="341"/>
+      <c r="BG31" s="341"/>
+      <c r="BH31" s="342"/>
       <c r="BI31" s="102"/>
     </row>
     <row r="32" spans="1:70" ht="15.95" customHeight="1" x14ac:dyDescent="0.5">
@@ -8465,8 +8468,8 @@
       <c r="AX34" s="188"/>
       <c r="AY34" s="188"/>
       <c r="AZ34" s="189"/>
-      <c r="BA34" s="339"/>
-      <c r="BB34" s="340"/>
+      <c r="BA34" s="338"/>
+      <c r="BB34" s="339"/>
       <c r="BC34" s="251"/>
       <c r="BD34" s="251"/>
       <c r="BE34" s="251"/>
@@ -8662,12 +8665,12 @@
       <c r="AZ37" s="255"/>
       <c r="BA37" s="245"/>
       <c r="BB37" s="246"/>
-      <c r="BC37" s="344"/>
-      <c r="BD37" s="344"/>
-      <c r="BE37" s="344"/>
-      <c r="BF37" s="344"/>
-      <c r="BG37" s="344"/>
-      <c r="BH37" s="345"/>
+      <c r="BC37" s="346"/>
+      <c r="BD37" s="346"/>
+      <c r="BE37" s="346"/>
+      <c r="BF37" s="346"/>
+      <c r="BG37" s="346"/>
+      <c r="BH37" s="347"/>
       <c r="BI37" s="102"/>
     </row>
     <row r="38" spans="1:61" ht="15.95" customHeight="1" x14ac:dyDescent="0.5">
@@ -8918,8 +8921,8 @@
       <c r="AX41" s="188"/>
       <c r="AY41" s="188"/>
       <c r="AZ41" s="189"/>
-      <c r="BA41" s="339"/>
-      <c r="BB41" s="340"/>
+      <c r="BA41" s="338"/>
+      <c r="BB41" s="339"/>
       <c r="BC41" s="251"/>
       <c r="BD41" s="251"/>
       <c r="BE41" s="251"/>
@@ -8983,12 +8986,12 @@
       <c r="AZ42" s="255"/>
       <c r="BA42" s="245"/>
       <c r="BB42" s="246"/>
-      <c r="BC42" s="344"/>
-      <c r="BD42" s="344"/>
-      <c r="BE42" s="344"/>
-      <c r="BF42" s="344"/>
-      <c r="BG42" s="344"/>
-      <c r="BH42" s="345"/>
+      <c r="BC42" s="346"/>
+      <c r="BD42" s="346"/>
+      <c r="BE42" s="346"/>
+      <c r="BF42" s="346"/>
+      <c r="BG42" s="346"/>
+      <c r="BH42" s="347"/>
       <c r="BI42" s="102"/>
     </row>
     <row r="43" spans="1:61" ht="15.95" customHeight="1" x14ac:dyDescent="0.5">
@@ -9045,8 +9048,8 @@
       <c r="AX43" s="188"/>
       <c r="AY43" s="188"/>
       <c r="AZ43" s="189"/>
-      <c r="BA43" s="339"/>
-      <c r="BB43" s="340"/>
+      <c r="BA43" s="338"/>
+      <c r="BB43" s="339"/>
       <c r="BC43" s="251"/>
       <c r="BD43" s="251"/>
       <c r="BE43" s="251"/>
@@ -9111,12 +9114,12 @@
       <c r="AZ44" s="255"/>
       <c r="BA44" s="245"/>
       <c r="BB44" s="246"/>
-      <c r="BC44" s="344"/>
-      <c r="BD44" s="344"/>
-      <c r="BE44" s="344"/>
-      <c r="BF44" s="344"/>
-      <c r="BG44" s="344"/>
-      <c r="BH44" s="345"/>
+      <c r="BC44" s="346"/>
+      <c r="BD44" s="346"/>
+      <c r="BE44" s="346"/>
+      <c r="BF44" s="346"/>
+      <c r="BG44" s="346"/>
+      <c r="BH44" s="347"/>
       <c r="BI44" s="102"/>
     </row>
     <row r="45" spans="1:61" ht="15.95" customHeight="1" x14ac:dyDescent="0.5">
@@ -9174,8 +9177,8 @@
       <c r="AX45" s="188"/>
       <c r="AY45" s="188"/>
       <c r="AZ45" s="189"/>
-      <c r="BA45" s="339"/>
-      <c r="BB45" s="340"/>
+      <c r="BA45" s="338"/>
+      <c r="BB45" s="339"/>
       <c r="BC45" s="251"/>
       <c r="BD45" s="251"/>
       <c r="BE45" s="251"/>
@@ -9633,12 +9636,12 @@
       <c r="AZ52" s="219"/>
       <c r="BA52" s="245"/>
       <c r="BB52" s="246"/>
-      <c r="BC52" s="344"/>
-      <c r="BD52" s="344"/>
-      <c r="BE52" s="344"/>
-      <c r="BF52" s="344"/>
-      <c r="BG52" s="344"/>
-      <c r="BH52" s="345"/>
+      <c r="BC52" s="346"/>
+      <c r="BD52" s="346"/>
+      <c r="BE52" s="346"/>
+      <c r="BF52" s="346"/>
+      <c r="BG52" s="346"/>
+      <c r="BH52" s="347"/>
       <c r="BI52" s="102"/>
     </row>
     <row r="53" spans="1:67" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -9736,7 +9739,7 @@
       </c>
       <c r="AR54" s="135"/>
       <c r="AS54" s="280">
-        <v>6271.56</v>
+        <v>4976</v>
       </c>
       <c r="AT54" s="281"/>
       <c r="AU54" s="281"/>
@@ -9746,7 +9749,7 @@
       <c r="AY54" s="281"/>
       <c r="AZ54" s="282"/>
       <c r="BA54" s="280">
-        <v>188.15</v>
+        <v>0</v>
       </c>
       <c r="BB54" s="281"/>
       <c r="BC54" s="281"/>
@@ -9754,7 +9757,7 @@
       <c r="BE54" s="281"/>
       <c r="BF54" s="281"/>
       <c r="BG54" s="281"/>
-      <c r="BH54" s="346"/>
+      <c r="BH54" s="348"/>
       <c r="BI54" s="102"/>
     </row>
     <row r="55" spans="1:67" ht="5.0999999999999996" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
@@ -9826,7 +9829,7 @@
         <v>37</v>
       </c>
       <c r="P56" s="239" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q56" s="240"/>
       <c r="R56" s="240"/>
@@ -11030,12 +11033,12 @@
       <c r="AF82" s="166"/>
       <c r="AG82" s="172">
         <f>AG8</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH82" s="173"/>
       <c r="AI82" s="173">
         <f>AI8</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ82" s="173"/>
       <c r="AK82" s="173">
@@ -11051,12 +11054,12 @@
       <c r="AO82" s="166"/>
       <c r="AP82" s="172">
         <f>AP8</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ82" s="173"/>
       <c r="AR82" s="173">
         <f>AR8</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS82" s="173"/>
       <c r="AT82" s="173">
@@ -11071,24 +11074,24 @@
       <c r="AW82" s="173"/>
       <c r="AX82" s="173">
         <f>AX8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY82" s="174"/>
       <c r="AZ82" s="166"/>
       <c r="BA82" s="172">
         <f>BA8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB82" s="173"/>
       <c r="BC82" s="173">
         <f>BC8</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BD82" s="174"/>
       <c r="BE82" s="166"/>
       <c r="BF82" s="226">
         <f>BF8</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BG82" s="227"/>
       <c r="BH82" s="102"/>
@@ -11134,7 +11137,7 @@
       </c>
       <c r="D84" s="328" t="str">
         <f>D10</f>
-        <v>บริษัท อ่างทองเคเบิลทีวี จำกัด</v>
+        <v>บริษัท อัลฟ่า ซัพพลาย จำกัด</v>
       </c>
       <c r="E84" s="328"/>
       <c r="F84" s="328"/>
@@ -11220,7 +11223,7 @@
       </c>
       <c r="D86" s="276" t="str">
         <f>D12</f>
-        <v>เลขที่ 18/2 ถนนอ่างทอง-สิงห์บุรี ตำบลตลาดหลวง อำเภอเมืองอ่างทอง จังหวัดอ่างทอง 14000</v>
+        <v>อาคาร - ห้องเลขที่ - ชั้นที่ - หมู่บ้าน - เลขที่ 35/3 หมู่ที่ 5 ถนน - ตำบลคอกกระบือ อำเภอเมืองสมุทรสาคร จังหวัดสมุทรสาคร 74000</v>
       </c>
       <c r="E86" s="276"/>
       <c r="F86" s="276"/>
@@ -11471,22 +11474,22 @@
       <c r="AF90" s="166"/>
       <c r="AG90" s="172">
         <f>AG16</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH90" s="173"/>
       <c r="AI90" s="173">
         <f>AI16</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AJ90" s="173"/>
       <c r="AK90" s="173">
         <f>AK16</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL90" s="173"/>
       <c r="AM90" s="173">
         <f>AM16</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN90" s="174"/>
       <c r="AO90" s="166"/>
@@ -11502,12 +11505,12 @@
       <c r="AS90" s="173"/>
       <c r="AT90" s="173">
         <f>AT16</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU90" s="173"/>
       <c r="AV90" s="173">
         <f>AV16</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AW90" s="173"/>
       <c r="AX90" s="173">
@@ -11518,18 +11521,18 @@
       <c r="AZ90" s="166"/>
       <c r="BA90" s="172">
         <f>BA16</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BB90" s="173"/>
       <c r="BC90" s="173">
         <f>BC16</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD90" s="174"/>
       <c r="BE90" s="166"/>
       <c r="BF90" s="226">
         <f>BF16</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BG90" s="227"/>
       <c r="BH90" s="102"/>
@@ -11575,7 +11578,7 @@
       </c>
       <c r="D92" s="231" t="str">
         <f>D18</f>
-        <v>นาย สงกรานต์ กลิ่นดอกไม้</v>
+        <v>นางสาว ภริตพร ขำต้นวงศ์</v>
       </c>
       <c r="E92" s="231"/>
       <c r="F92" s="231"/>
@@ -11661,7 +11664,7 @@
       </c>
       <c r="D94" s="276" t="str">
         <f>D20</f>
-        <v>เลขที่ 18/2 ถนนอ่างทอง-สิงห์บุรี ตำบลตลาดหลวง อำเภอเมืองอ่างทอง จังหวัดอ่างทอง 14000</v>
+        <v>989 ซ.เพรชเกษม 79 หนองแขม หนองแขม กรุงเทพมหานคร 10160</v>
       </c>
       <c r="E94" s="276"/>
       <c r="F94" s="276"/>
@@ -12220,7 +12223,7 @@
       <c r="AJ104" s="93"/>
       <c r="AK104" s="256" t="str">
         <f>IF(AK30="","",AK30)</f>
-        <v/>
+        <v>31/12/2025</v>
       </c>
       <c r="AL104" s="257"/>
       <c r="AM104" s="257"/>
@@ -12229,9 +12232,9 @@
       <c r="AP104" s="257"/>
       <c r="AQ104" s="257"/>
       <c r="AR104" s="258"/>
-      <c r="AS104" s="304" t="str">
+      <c r="AS104" s="304">
         <f>IF(AS30="","",AS30)</f>
-        <v/>
+        <v>4976</v>
       </c>
       <c r="AT104" s="305"/>
       <c r="AU104" s="305"/>
@@ -12296,7 +12299,7 @@
       <c r="AJ105" s="93"/>
       <c r="AK105" s="301" t="str">
         <f>IF(AK31="","",AK31)</f>
-        <v>31/12/2025</v>
+        <v/>
       </c>
       <c r="AL105" s="302"/>
       <c r="AM105" s="302"/>
@@ -12305,9 +12308,9 @@
       <c r="AP105" s="302"/>
       <c r="AQ105" s="302"/>
       <c r="AR105" s="303"/>
-      <c r="AS105" s="292">
+      <c r="AS105" s="292" t="str">
         <f>IF(AS31="","",AS31)</f>
-        <v>6271.56</v>
+        <v/>
       </c>
       <c r="AT105" s="293"/>
       <c r="AU105" s="293"/>
@@ -12316,9 +12319,9 @@
       <c r="AX105" s="293"/>
       <c r="AY105" s="293"/>
       <c r="AZ105" s="294"/>
-      <c r="BA105" s="170">
+      <c r="BA105" s="170" t="str">
         <f>IF(BA31="","",BA31)</f>
-        <v>188.15</v>
+        <v/>
       </c>
       <c r="BB105" s="171"/>
       <c r="BC105" s="215" t="str">
@@ -14115,7 +14118,7 @@
       <c r="AR128" s="135"/>
       <c r="AS128" s="329">
         <f>SUM(AS104:AS126)</f>
-        <v>6271.56</v>
+        <v>4976</v>
       </c>
       <c r="AT128" s="330"/>
       <c r="AU128" s="330"/>
